--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_45.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_45.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5690103.094607378</v>
+        <v>5730040.273382459</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.318645785</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645786</v>
+        <v>6767152.318645785</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517483</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517483</v>
+        <v>2916902.906517485</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>174.6089458300096</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>100.6192915779626</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -684,16 +684,16 @@
         <v>814</v>
       </c>
       <c r="L2" t="n">
-        <v>507.7400371911698</v>
+        <v>814</v>
       </c>
       <c r="M2" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N2" t="n">
-        <v>814</v>
+        <v>194.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>313.1545016101228</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -705,16 +705,16 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
-        <v>249.2212965486107</v>
+        <v>649.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>638.3734759809475</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>241.2078457259397</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -748,10 +748,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>308.4311513056531</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617061031</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>320.9396782847054</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -894,49 +894,49 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>347.8515213095984</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>404.8896287080119</v>
+        <v>98.45902009342628</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>184.3147947600191</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
       </c>
       <c r="M5" t="n">
-        <v>297.9910820919849</v>
+        <v>814</v>
       </c>
       <c r="N5" t="n">
         <v>194.5855355810472</v>
       </c>
       <c r="O5" t="n">
-        <v>313.1545016101228</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>370.9706110579117</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y5" t="n">
         <v>111.3174326828064</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>547.2737972923793</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>90.0987672932513</v>
+        <v>355.9195897572523</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061019</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269237</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1128,34 +1128,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C8" t="n">
         <v>449.4745782429939</v>
       </c>
       <c r="D8" t="n">
-        <v>353.8273874425797</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.75737228701621</v>
+        <v>97.3267636724309</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>313.1545016101269</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -1167,10 +1167,10 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>216.0296191332216</v>
       </c>
       <c r="Q8" t="n">
         <v>370.9706110579117</v>
@@ -1182,7 +1182,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1194,7 +1194,7 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1219,10 +1219,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>118.0893820455458</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1261,19 +1261,19 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>5.357765217513816</v>
+        <v>63.08338960093648</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>91.42153354832249</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269246</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1371,13 +1371,13 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>368.8164552821566</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
         <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>213.1084678514908</v>
       </c>
     </row>
     <row r="12">
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>282.0825727406839</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>322.1057364857073</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1659,13 +1659,13 @@
         <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>5.790687934024772</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>378.8510241668239</v>
+        <v>373.7938915331859</v>
       </c>
       <c r="W14" t="n">
-        <v>387.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>341.2818334606677</v>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1793,22 +1793,22 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>269.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>18.44220111900162</v>
       </c>
       <c r="P16" t="n">
-        <v>258.9489357531582</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>361.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>361.2138452671574</v>
       </c>
       <c r="R19" t="n">
-        <v>9.811216319127904</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2145,7 +2145,7 @@
         <v>313.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>231.8868240682205</v>
+        <v>232.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>102.2523070907278</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>169.0507294048855</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -2319,7 +2319,7 @@
         <v>170.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>130.9085471252638</v>
+        <v>131.3391557398498</v>
       </c>
       <c r="E23" t="n">
         <v>125.3632896068686</v>
@@ -2328,7 +2328,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>124.7573722870162</v>
+        <v>124.3267636724302</v>
       </c>
       <c r="H23" t="n">
         <v>129.0096587035274</v>
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>404.1461227518799</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.2535386422013718</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>83.51170138942324</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>111.0266631814759</v>
       </c>
     </row>
     <row r="27">
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2744,10 +2744,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>208.5472557260005</v>
       </c>
       <c r="O28" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>256.9993129555745</v>
+        <v>189.5363985716396</v>
       </c>
       <c r="C29" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>178.7573722870162</v>
@@ -2838,16 +2838,16 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>189.8070437992264</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W29" t="n">
         <v>413.3734759809475</v>
@@ -2951,10 +2951,10 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>225.6324864347253</v>
       </c>
       <c r="O31" t="n">
-        <v>319.7059638971298</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3048,28 +3048,28 @@
         <v>8.45659138541424</v>
       </c>
       <c r="J32" t="n">
-        <v>377.7382696589756</v>
+        <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>351.8156858380821</v>
+        <v>351.8156858380793</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920268</v>
+        <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>153.5855355810893</v>
+        <v>153.5855355810884</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>329.9706110579538</v>
+        <v>329.9706110579529</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -3212,22 +3212,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>131.3113244366776</v>
       </c>
       <c r="N34" t="n">
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>225.4675834971362</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3285,34 +3285,34 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>377.7382696589829</v>
+        <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>773</v>
+        <v>10.23281455289469</v>
       </c>
       <c r="L35" t="n">
-        <v>351.8156858378721</v>
+        <v>598.5739533769372</v>
       </c>
       <c r="M35" t="n">
-        <v>256.991082092034</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>153.5855355810966</v>
+        <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>329.970611057961</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>203.8481678023229</v>
+        <v>212.3047591877378</v>
       </c>
       <c r="T35" t="n">
         <v>295.6755817285639</v>
@@ -3455,22 +3455,22 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>154.0941037942573</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>194.5984637871032</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3519,34 +3519,34 @@
         <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
-        <v>8.45659138541424</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>757.6173000000554</v>
+        <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>10.23281455320825</v>
+        <v>505.4012214191095</v>
       </c>
       <c r="L38" t="n">
-        <v>307.0571520018008</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>256.9910820920413</v>
+        <v>256.9910820920404</v>
       </c>
       <c r="N38" t="n">
-        <v>153.5855355811038</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>757.6173000000553</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3689,25 +3689,25 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>37.83128173769179</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>361.4147497128579</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,10 +3738,10 @@
         <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>81.41167584538807</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>281.8481678023229</v>
@@ -3792,10 +3792,10 @@
         <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>436.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>152.7818304157293</v>
       </c>
       <c r="W41" t="n">
         <v>425.3734759809475</v>
@@ -3814,28 +3814,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>171.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>148.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>134.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>129.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>126.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>95.51236190063754</v>
+        <v>112.7395358750273</v>
       </c>
       <c r="H42" t="n">
         <v>119.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>4.126385891348534</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>111.5684354475268</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3902,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>60.98864983028059</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3932,13 +3932,13 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>209.8370533926488</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>273.7419255901463</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.9993129555745</v>
+        <v>260.9178553864012</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>223.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>217.3632896068686</v>
@@ -3987,7 +3987,7 @@
         <v>217.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4020,25 +4020,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>399.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>462.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>226.7365483279485</v>
+        <v>442.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>451.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>324.3174326828064</v>
@@ -4054,19 +4054,19 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>145.1680871864211</v>
@@ -4102,16 +4102,16 @@
         <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>147.9181834781389</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>218.3577652175138</v>
       </c>
       <c r="U45" t="n">
         <v>213.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>227.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>245.3731429098285</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>121.7354699098466</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>152.4251080029341</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>298.3673161322752</v>
+        <v>391.9123998438258</v>
       </c>
       <c r="C2" t="n">
-        <v>248.3929946747056</v>
+        <v>341.9380783862562</v>
       </c>
       <c r="D2" t="n">
-        <v>237.9494030182917</v>
+        <v>331.4944867298423</v>
       </c>
       <c r="E2" t="n">
-        <v>233.5420397790304</v>
+        <v>327.0871234905811</v>
       </c>
       <c r="F2" t="n">
-        <v>228.6030208820488</v>
+        <v>322.1481045935994</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8076953396081</v>
+        <v>318.3527790511588</v>
       </c>
       <c r="H2" t="n">
         <v>216.7171309926107</v>
@@ -4327,13 +4327,13 @@
         <v>431.6498286273397</v>
       </c>
       <c r="L2" t="n">
-        <v>724.6411041918145</v>
+        <v>415.2876064051174</v>
       </c>
       <c r="M2" t="n">
-        <v>1229.500011169607</v>
+        <v>920.1465133829104</v>
       </c>
       <c r="N2" t="n">
-        <v>1213.137788947385</v>
+        <v>1529.455467341449</v>
       </c>
       <c r="O2" t="n">
         <v>2018.997788947385</v>
@@ -4348,13 +4348,13 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2502.740639767053</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>1910.139042061433</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U2" t="n">
-        <v>1658.400358678998</v>
+        <v>2062.440762719402</v>
       </c>
       <c r="V2" t="n">
         <v>1426.227606995337</v>
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2563.531449951958</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C3" t="n">
-        <v>2563.531449951958</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D3" t="n">
-        <v>2319.887161339897</v>
+        <v>931.509519579215</v>
       </c>
       <c r="E3" t="n">
-        <v>2319.887161339897</v>
+        <v>931.509519579215</v>
       </c>
       <c r="F3" t="n">
-        <v>2319.887161339897</v>
+        <v>931.509519579215</v>
       </c>
       <c r="G3" t="n">
-        <v>2319.887161339897</v>
+        <v>619.9629020987572</v>
       </c>
       <c r="H3" t="n">
-        <v>2319.887161339897</v>
+        <v>284.4395817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>2100.567579631464</v>
+        <v>65.12</v>
       </c>
       <c r="J3" t="n">
-        <v>2224.524099806763</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>2413.716915901147</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>2685.067377496347</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M3" t="n">
-        <v>2771.147919239206</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>2904.428203846775</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O3" t="n">
-        <v>3143.470655530493</v>
+        <v>1108.023075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>3256</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>3107.238588593556</v>
+        <v>1071.791008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>3040.002224992939</v>
+        <v>1004.554645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>3034.590340934844</v>
+        <v>999.1427613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>3034.377856328595</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V3" t="n">
-        <v>3019.720616741201</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W3" t="n">
-        <v>2987.020472387838</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>2966.957099210679</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y3" t="n">
-        <v>2563.531449951958</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>462.3368525126554</v>
+        <v>767.6406774199726</v>
       </c>
       <c r="C4" t="n">
-        <v>462.3368525126554</v>
+        <v>767.6406774199726</v>
       </c>
       <c r="D4" t="n">
-        <v>575.6559966376554</v>
+        <v>767.6406774199726</v>
       </c>
       <c r="E4" t="n">
-        <v>693.4849008490685</v>
+        <v>767.6406774199726</v>
       </c>
       <c r="F4" t="n">
-        <v>693.4849008490685</v>
+        <v>892.0016500119081</v>
       </c>
       <c r="G4" t="n">
-        <v>846.8914667359537</v>
+        <v>1045.408215898793</v>
       </c>
       <c r="H4" t="n">
-        <v>1016.408051895351</v>
+        <v>1214.924801058191</v>
       </c>
       <c r="I4" t="n">
-        <v>1237.540930831434</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="J4" t="n">
-        <v>1436.057679994273</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1424.572001403314</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1251.657783957168</v>
       </c>
       <c r="O4" t="n">
-        <v>1014.503122964673</v>
+        <v>1008.783476806647</v>
       </c>
       <c r="P4" t="n">
-        <v>724.1517115219688</v>
+        <v>718.4320653639429</v>
       </c>
       <c r="Q4" t="n">
-        <v>395.0211393749001</v>
+        <v>389.3014932168742</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4509,22 +4509,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T4" t="n">
-        <v>290.445934252978</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>290.445934252978</v>
+        <v>348.9214477324598</v>
       </c>
       <c r="V4" t="n">
-        <v>290.445934252978</v>
+        <v>484.3404584812628</v>
       </c>
       <c r="W4" t="n">
-        <v>462.3368525126554</v>
+        <v>656.2313767409403</v>
       </c>
       <c r="X4" t="n">
-        <v>462.3368525126554</v>
+        <v>656.2313767409403</v>
       </c>
       <c r="Y4" t="n">
-        <v>462.3368525126554</v>
+        <v>767.6406774199726</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1857.446338054225</v>
+        <v>1453.405934013821</v>
       </c>
       <c r="C5" t="n">
         <v>1403.431612556251</v>
       </c>
       <c r="D5" t="n">
-        <v>988.9476168594329</v>
+        <v>1392.988020899837</v>
       </c>
       <c r="E5" t="n">
-        <v>637.5824438194345</v>
+        <v>984.5402536201717</v>
       </c>
       <c r="F5" t="n">
-        <v>228.6030208820488</v>
+        <v>885.0866979702462</v>
       </c>
       <c r="G5" t="n">
-        <v>224.8076953396081</v>
+        <v>477.2509683874014</v>
       </c>
       <c r="H5" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I5" t="n">
         <v>65.12</v>
@@ -4561,22 +4561,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6498286273397</v>
+        <v>1067.695490485906</v>
       </c>
       <c r="L5" t="n">
-        <v>415.2876064051174</v>
+        <v>1051.333268263684</v>
       </c>
       <c r="M5" t="n">
-        <v>920.1465133829104</v>
+        <v>1034.971046041462</v>
       </c>
       <c r="N5" t="n">
-        <v>1529.455467341449</v>
+        <v>1644.28</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2450.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2824.857788947385</v>
+        <v>3256</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
@@ -4600,10 +4600,10 @@
         <v>2246.939852295688</v>
       </c>
       <c r="X5" t="n">
-        <v>2052.715778092993</v>
+        <v>1648.675374052589</v>
       </c>
       <c r="Y5" t="n">
-        <v>1940.273926898239</v>
+        <v>1536.233522857835</v>
       </c>
     </row>
     <row r="6">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C6" t="n">
         <v>65.12</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>667.7506049216878</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S6" t="n">
-        <v>600.5142413210704</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T6" t="n">
-        <v>595.1023572629756</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U6" t="n">
-        <v>594.8898726567263</v>
+        <v>824.1027362016963</v>
       </c>
       <c r="V6" t="n">
-        <v>580.2326330693322</v>
+        <v>809.4454966143022</v>
       </c>
       <c r="W6" t="n">
-        <v>489.2237772175632</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y6" t="n">
-        <v>65.12</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>613.3676435368488</v>
+        <v>293.2377926425189</v>
       </c>
       <c r="C7" t="n">
-        <v>739.3696493552847</v>
+        <v>293.2377926425189</v>
       </c>
       <c r="D7" t="n">
-        <v>852.6887934802847</v>
+        <v>406.5569367675189</v>
       </c>
       <c r="E7" t="n">
-        <v>970.5176976916978</v>
+        <v>406.5569367675189</v>
       </c>
       <c r="F7" t="n">
-        <v>970.5176976916978</v>
+        <v>530.9179093594545</v>
       </c>
       <c r="G7" t="n">
-        <v>1123.924263578583</v>
+        <v>684.3244752463397</v>
       </c>
       <c r="H7" t="n">
-        <v>1123.924263578583</v>
+        <v>853.8410604057373</v>
       </c>
       <c r="I7" t="n">
-        <v>1345.057142514666</v>
+        <v>1074.97393934182</v>
       </c>
       <c r="J7" t="n">
         <v>1436.057679994271</v>
@@ -4722,22 +4722,22 @@
         <v>1546.42211393114</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.42211393114</v>
+        <v>1522.636630943484</v>
       </c>
       <c r="M7" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415656</v>
       </c>
       <c r="N7" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.872300969509</v>
       </c>
       <c r="O7" t="n">
-        <v>1014.503122964673</v>
+        <v>984.9979938189891</v>
       </c>
       <c r="P7" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762846</v>
       </c>
       <c r="Q7" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292159</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
@@ -4746,22 +4746,22 @@
         <v>102.3702550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>290.445934252978</v>
+        <v>181.4804549762267</v>
       </c>
       <c r="U7" t="n">
-        <v>290.445934252978</v>
+        <v>181.4804549762267</v>
       </c>
       <c r="V7" t="n">
-        <v>290.445934252978</v>
+        <v>181.4804549762267</v>
       </c>
       <c r="W7" t="n">
-        <v>462.3368525126554</v>
+        <v>181.4804549762267</v>
       </c>
       <c r="X7" t="n">
-        <v>613.3676435368488</v>
+        <v>181.4804549762267</v>
       </c>
       <c r="Y7" t="n">
-        <v>613.3676435368488</v>
+        <v>181.4804549762267</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1857.446338054225</v>
+        <v>645.3251259330127</v>
       </c>
       <c r="C8" t="n">
-        <v>1403.431612556251</v>
+        <v>191.310400435039</v>
       </c>
       <c r="D8" t="n">
-        <v>1046.0302110991</v>
+        <v>180.8668087786251</v>
       </c>
       <c r="E8" t="n">
-        <v>637.5824438194345</v>
+        <v>176.4594455393638</v>
       </c>
       <c r="F8" t="n">
-        <v>228.6030208820488</v>
+        <v>171.5204266423821</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>73.21056434699739</v>
       </c>
       <c r="H8" t="n">
-        <v>216.7171309926107</v>
+        <v>65.12</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
@@ -4798,19 +4798,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>937.5543724554943</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>921.1921502332721</v>
+        <v>1139.40388673148</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.051057211065</v>
+        <v>1644.262793709273</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169603</v>
+        <v>2253.571747667811</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169603</v>
+        <v>2237.209525445589</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4825,22 +4825,22 @@
         <v>3160.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2971.632576231427</v>
+        <v>2567.592172191024</v>
       </c>
       <c r="U8" t="n">
-        <v>2719.893892848992</v>
+        <v>2315.853488808589</v>
       </c>
       <c r="V8" t="n">
-        <v>2487.721141165332</v>
+        <v>2083.680737124928</v>
       </c>
       <c r="W8" t="n">
-        <v>2246.939852295688</v>
+        <v>1842.899448255284</v>
       </c>
       <c r="X8" t="n">
-        <v>2052.715778092993</v>
+        <v>1244.634970012185</v>
       </c>
       <c r="Y8" t="n">
-        <v>1940.273926898239</v>
+        <v>1132.193118817431</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
       <c r="C9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
       <c r="D9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
       <c r="E9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
       <c r="F9" t="n">
-        <v>184.4022040864099</v>
+        <v>65.12</v>
       </c>
       <c r="G9" t="n">
         <v>65.12</v>
@@ -4904,22 +4904,22 @@
         <v>1004.554645361474</v>
       </c>
       <c r="T9" t="n">
-        <v>999.1427613033796</v>
+        <v>940.8340498049729</v>
       </c>
       <c r="U9" t="n">
-        <v>998.9302766971304</v>
+        <v>940.6215651987236</v>
       </c>
       <c r="V9" t="n">
-        <v>984.2730371097363</v>
+        <v>521.9239215709254</v>
       </c>
       <c r="W9" t="n">
-        <v>547.53248871597</v>
+        <v>489.2237772175632</v>
       </c>
       <c r="X9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.4691155388108</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>663.7399247700198</v>
+        <v>847.2799956093145</v>
       </c>
       <c r="C10" t="n">
-        <v>789.7419305884556</v>
+        <v>973.2820014277503</v>
       </c>
       <c r="D10" t="n">
-        <v>789.7419305884556</v>
+        <v>988.7735563560526</v>
       </c>
       <c r="E10" t="n">
-        <v>907.5708347998686</v>
+        <v>988.7735563560526</v>
       </c>
       <c r="F10" t="n">
-        <v>1031.931807391804</v>
+        <v>1113.134528947988</v>
       </c>
       <c r="G10" t="n">
-        <v>1185.338373278689</v>
+        <v>1266.541094834874</v>
       </c>
       <c r="H10" t="n">
-        <v>1185.338373278689</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="I10" t="n">
-        <v>1185.338373278689</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.422113931141</v>
+        <v>1436.057679994271</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.42211393114</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943485</v>
+        <v>1522.636630943484</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.786518415657</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.87230096951</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>984.99799381899</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762856</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292168</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>65.12</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>133.5404762057636</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="U10" t="n">
-        <v>380.0916688440502</v>
+        <v>102.3702550941731</v>
       </c>
       <c r="V10" t="n">
-        <v>380.0916688440502</v>
+        <v>301.1916479801191</v>
       </c>
       <c r="W10" t="n">
-        <v>551.9825871037276</v>
+        <v>473.0825662397965</v>
       </c>
       <c r="X10" t="n">
-        <v>551.9825871037276</v>
+        <v>624.11335726399</v>
       </c>
       <c r="Y10" t="n">
-        <v>551.9825871037276</v>
+        <v>735.5226579430223</v>
       </c>
     </row>
     <row r="11">
@@ -5008,16 +5008,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>838.4582816569759</v>
+        <v>1207.376245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>611.7162834317296</v>
+        <v>980.6342475204788</v>
       </c>
       <c r="D11" t="n">
-        <v>611.7162834317296</v>
+        <v>793.4229790963881</v>
       </c>
       <c r="E11" t="n">
-        <v>430.5412434247916</v>
+        <v>612.24793908945</v>
       </c>
       <c r="F11" t="n">
         <v>430.5412434247916</v>
@@ -5038,46 +5038,46 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1326.070851496302</v>
+        <v>1500.692076218397</v>
       </c>
       <c r="M11" t="n">
-        <v>1836.919680225237</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>2450.14</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2450.14</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3256</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3229.860001183541</v>
+        <v>3256</v>
       </c>
       <c r="S11" t="n">
-        <v>2957.286094312508</v>
+        <v>3256</v>
       </c>
       <c r="T11" t="n">
-        <v>2957.286094312508</v>
+        <v>2890.671129567107</v>
       </c>
       <c r="U11" t="n">
-        <v>2584.744220290127</v>
+        <v>2462.164769416995</v>
       </c>
       <c r="V11" t="n">
-        <v>2175.80379183879</v>
+        <v>2053.224340965658</v>
       </c>
       <c r="W11" t="n">
-        <v>1758.25482620147</v>
+        <v>2053.224340965658</v>
       </c>
       <c r="X11" t="n">
-        <v>1387.263075231098</v>
+        <v>1682.232589995286</v>
       </c>
       <c r="Y11" t="n">
-        <v>1098.053547268667</v>
+        <v>1466.971511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5108,28 +5108,28 @@
         <v>65.12</v>
       </c>
       <c r="I12" t="n">
-        <v>65.12</v>
+        <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>411.826520175299</v>
+        <v>419.6213981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>823.7693362696824</v>
+        <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1317.869797864882</v>
+        <v>1325.664675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1626.700339607742</v>
+        <v>1634.495217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1786.701204729125</v>
+        <v>1990.525502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2248.493656412844</v>
+        <v>2299.895183973269</v>
       </c>
       <c r="P12" t="n">
-        <v>2583.773000882351</v>
+        <v>2635.174528442776</v>
       </c>
       <c r="Q12" t="n">
         <v>2635.174528442776</v>
@@ -5166,52 +5166,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="C13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="D13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="E13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="F13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="G13" t="n">
-        <v>114.3352720687222</v>
+        <v>158.5719284794718</v>
       </c>
       <c r="H13" t="n">
-        <v>114.3352720687222</v>
+        <v>154.7627101950085</v>
       </c>
       <c r="I13" t="n">
-        <v>162.2181510048052</v>
+        <v>202.6455891310914</v>
       </c>
       <c r="J13" t="n">
-        <v>350.0518916572565</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="K13" t="n">
-        <v>350.0518916572565</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="L13" t="n">
-        <v>350.0518916572565</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="M13" t="n">
-        <v>350.0518916572565</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="N13" t="n">
-        <v>350.0518916572565</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="O13" t="n">
-        <v>65.12</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="P13" t="n">
-        <v>65.12</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>390.4793297835428</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5229,13 +5229,13 @@
         <v>178.8182646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="X13" t="n">
-        <v>177.4315880782802</v>
+        <v>178.8182646830375</v>
       </c>
       <c r="Y13" t="n">
-        <v>114.3352720687222</v>
+        <v>178.8182646830375</v>
       </c>
     </row>
     <row r="14">
@@ -5269,25 +5269,25 @@
         <v>65.12</v>
       </c>
       <c r="J14" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K14" t="n">
-        <v>1166.135479385524</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L14" t="n">
-        <v>1166.135479385524</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M14" t="n">
-        <v>1676.984308114459</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N14" t="n">
-        <v>2290.204627889222</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O14" t="n">
-        <v>2290.204627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>3096.064627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3256</v>
@@ -5302,10 +5302,10 @@
         <v>2670.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>2664.773295489988</v>
+        <v>2268.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>2282.095493301277</v>
+        <v>1890.809153926582</v>
       </c>
       <c r="W14" t="n">
         <v>1890.809153926582</v>
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1628.625837177891</v>
+        <v>613.8609716812728</v>
       </c>
       <c r="C15" t="n">
-        <v>1517.413804404639</v>
+        <v>502.6489389080209</v>
       </c>
       <c r="D15" t="n">
-        <v>1419.496948952414</v>
+        <v>404.732083455796</v>
       </c>
       <c r="E15" t="n">
-        <v>1326.898870950482</v>
+        <v>312.134005453864</v>
       </c>
       <c r="F15" t="n">
-        <v>1237.367313033435</v>
+        <v>222.6024475368167</v>
       </c>
       <c r="G15" t="n">
-        <v>1161.872832351589</v>
+        <v>147.1079668549709</v>
       </c>
       <c r="H15" t="n">
-        <v>1079.884865496618</v>
+        <v>65.12</v>
       </c>
       <c r="I15" t="n">
-        <v>1113.419743464183</v>
+        <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>1401.912572246338</v>
+        <v>464.2892343101461</v>
       </c>
       <c r="K15" t="n">
-        <v>1591.105388340722</v>
+        <v>653.4820504045294</v>
       </c>
       <c r="L15" t="n">
-        <v>1862.455849935922</v>
+        <v>1173.32251199973</v>
       </c>
       <c r="M15" t="n">
-        <v>2197.026391678781</v>
+        <v>1507.893053742589</v>
       </c>
       <c r="N15" t="n">
-        <v>2578.796676286349</v>
+        <v>1889.663338350157</v>
       </c>
       <c r="O15" t="n">
-        <v>2817.839127970068</v>
+        <v>2128.705790033876</v>
       </c>
       <c r="P15" t="n">
-        <v>3178.858472439575</v>
+        <v>2241.235134503383</v>
       </c>
       <c r="Q15" t="n">
-        <v>3256</v>
+        <v>2241.235134503383</v>
       </c>
       <c r="R15" t="n">
-        <v>2956.733538088506</v>
+        <v>1941.968672591888</v>
       </c>
       <c r="S15" t="n">
-        <v>2738.992123982838</v>
+        <v>1724.22725848622</v>
       </c>
       <c r="T15" t="n">
-        <v>2583.075189419692</v>
+        <v>1568.310323923075</v>
       </c>
       <c r="U15" t="n">
-        <v>2432.357654308393</v>
+        <v>1417.592788811775</v>
       </c>
       <c r="V15" t="n">
-        <v>2267.195364215948</v>
+        <v>1252.43049871933</v>
       </c>
       <c r="W15" t="n">
-        <v>2083.990169357536</v>
+        <v>1069.225303860918</v>
       </c>
       <c r="X15" t="n">
-        <v>1913.421745675326</v>
+        <v>898.6568801787081</v>
       </c>
       <c r="Y15" t="n">
-        <v>1763.531449951958</v>
+        <v>748.7665844553401</v>
       </c>
     </row>
     <row r="16">
@@ -5409,46 +5409,46 @@
         <v>283.9399739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>283.9399739669084</v>
+        <v>249.054905223923</v>
       </c>
       <c r="E16" t="n">
-        <v>283.9399739669084</v>
+        <v>249.054905223923</v>
       </c>
       <c r="F16" t="n">
-        <v>283.9399739669084</v>
+        <v>249.054905223923</v>
       </c>
       <c r="G16" t="n">
-        <v>289.8365398537936</v>
+        <v>254.9514711108083</v>
       </c>
       <c r="H16" t="n">
-        <v>311.8431250131912</v>
+        <v>276.9580562702059</v>
       </c>
       <c r="I16" t="n">
-        <v>385.4660039492741</v>
+        <v>350.5809352062888</v>
       </c>
       <c r="J16" t="n">
-        <v>599.0397446017254</v>
+        <v>564.1546758587401</v>
       </c>
       <c r="K16" t="n">
-        <v>599.0397446017254</v>
+        <v>564.1546758587401</v>
       </c>
       <c r="L16" t="n">
-        <v>599.0397446017254</v>
+        <v>564.1546758587401</v>
       </c>
       <c r="M16" t="n">
-        <v>326.6845815688467</v>
+        <v>564.1546758587401</v>
       </c>
       <c r="N16" t="n">
-        <v>326.6845815688467</v>
+        <v>564.1546758587401</v>
       </c>
       <c r="O16" t="n">
-        <v>326.6845815688467</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="P16" t="n">
-        <v>65.12</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5506,22 +5506,22 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.135479385524</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L17" t="n">
-        <v>1166.135479385524</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M17" t="n">
-        <v>1676.984308114459</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N17" t="n">
-        <v>2290.204627889222</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O17" t="n">
-        <v>2290.204627889222</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>2817.400904947332</v>
@@ -5585,25 +5585,25 @@
         <v>126.374877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>526.5413981428638</v>
+        <v>250.3313981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>715.7342142372472</v>
+        <v>715.7342142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>1246.060087757305</v>
+        <v>987.0846758324474</v>
       </c>
       <c r="M18" t="n">
-        <v>1332.140629500164</v>
+        <v>1073.165217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1465.420914107732</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O18" t="n">
-        <v>1704.463365791451</v>
+        <v>1445.487953866594</v>
       </c>
       <c r="P18" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5640,52 +5640,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>422.5399739669084</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C19" t="n">
-        <v>428.7519797853442</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D19" t="n">
-        <v>422.1497393251871</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="E19" t="n">
-        <v>422.1497393251871</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="F19" t="n">
-        <v>426.7207119171226</v>
+        <v>416.5763329969353</v>
       </c>
       <c r="G19" t="n">
-        <v>460.3372778040079</v>
+        <v>450.1928988838205</v>
       </c>
       <c r="H19" t="n">
-        <v>510.0638629634055</v>
+        <v>499.9194840432181</v>
       </c>
       <c r="I19" t="n">
-        <v>611.4067418994885</v>
+        <v>601.2623629793011</v>
       </c>
       <c r="J19" t="n">
-        <v>852.7004825519398</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="K19" t="n">
-        <v>852.7004825519398</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="L19" t="n">
-        <v>852.7004825519398</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="M19" t="n">
-        <v>852.7004825519398</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="N19" t="n">
-        <v>852.7004825519398</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="O19" t="n">
-        <v>487.6039531791974</v>
+        <v>842.5561036317524</v>
       </c>
       <c r="P19" t="n">
-        <v>75.03031951427062</v>
+        <v>429.9824699668256</v>
       </c>
       <c r="Q19" t="n">
-        <v>75.03031951427062</v>
+        <v>65.12</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5709,7 +5709,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
     </row>
     <row r="20">
@@ -5746,16 +5746,16 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>456.4291130376557</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>456.4291130376557</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M20" t="n">
-        <v>592.460585172569</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="N20" t="n">
-        <v>1205.680904947332</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="O20" t="n">
         <v>2011.540904947332</v>
@@ -5770,22 +5770,22 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184576</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
         <v>1085.153329539235</v>
@@ -5819,28 +5819,28 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>109.1402898924222</v>
+        <v>65.12</v>
       </c>
       <c r="J21" t="n">
-        <v>509.3068100677211</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>698.4996261621045</v>
+        <v>654.4793362696823</v>
       </c>
       <c r="L21" t="n">
-        <v>969.8500877573045</v>
+        <v>925.8297978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>1055.930629500164</v>
+        <v>1011.910339607742</v>
       </c>
       <c r="N21" t="n">
-        <v>1189.210914107732</v>
+        <v>1145.19062421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1704.463365791451</v>
+        <v>1384.233075899029</v>
       </c>
       <c r="P21" t="n">
-        <v>1816.992710260958</v>
+        <v>1772.972420368535</v>
       </c>
       <c r="Q21" t="n">
         <v>1816.992710260958</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
       <c r="C22" t="n">
-        <v>428.7519797853442</v>
+        <v>420.2011183212408</v>
       </c>
       <c r="D22" t="n">
-        <v>428.7519797853442</v>
+        <v>420.2011183212408</v>
       </c>
       <c r="E22" t="n">
-        <v>428.7519797853442</v>
+        <v>420.2011183212408</v>
       </c>
       <c r="F22" t="n">
-        <v>433.3229523772797</v>
+        <v>424.7720909131763</v>
       </c>
       <c r="G22" t="n">
-        <v>466.939518264165</v>
+        <v>458.3886568000616</v>
       </c>
       <c r="H22" t="n">
-        <v>516.6661034235625</v>
+        <v>508.1152419594592</v>
       </c>
       <c r="I22" t="n">
-        <v>618.0089823596454</v>
+        <v>609.4581208955422</v>
       </c>
       <c r="J22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.7518615479935</v>
       </c>
       <c r="K22" t="n">
-        <v>859.3027230120967</v>
+        <v>850.7518615479935</v>
       </c>
       <c r="L22" t="n">
-        <v>859.3027230120967</v>
+        <v>704.7441563381155</v>
       </c>
       <c r="M22" t="n">
-        <v>615.2303882620463</v>
+        <v>704.7441563381155</v>
       </c>
       <c r="N22" t="n">
-        <v>320.0939485936777</v>
+        <v>704.7441563381155</v>
       </c>
       <c r="O22" t="n">
-        <v>320.0939485936777</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="P22" t="n">
-        <v>320.0939485936777</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="Q22" t="n">
-        <v>320.0939485936777</v>
+        <v>601.4589976606127</v>
       </c>
       <c r="R22" t="n">
         <v>149.3356360634903</v>
@@ -5946,7 +5946,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
     </row>
     <row r="23">
@@ -5962,13 +5962,13 @@
         <v>707.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F23" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G23" t="n">
         <v>195.4327865692196</v>
@@ -5983,22 +5983,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1166.135479385524</v>
+        <v>520.2108514963016</v>
       </c>
       <c r="L23" t="n">
-        <v>1166.135479385524</v>
+        <v>520.2108514963016</v>
       </c>
       <c r="M23" t="n">
-        <v>1676.984308114459</v>
+        <v>1031.059680225237</v>
       </c>
       <c r="N23" t="n">
-        <v>2011.540904947332</v>
+        <v>1644.28</v>
       </c>
       <c r="O23" t="n">
-        <v>2011.540904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="P23" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q23" t="n">
         <v>3256</v>
@@ -6056,19 +6056,19 @@
         <v>65.12</v>
       </c>
       <c r="I24" t="n">
-        <v>109.1402898924222</v>
+        <v>65.12</v>
       </c>
       <c r="J24" t="n">
-        <v>233.0968100677211</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K24" t="n">
-        <v>422.2896261621045</v>
+        <v>654.4793362696823</v>
       </c>
       <c r="L24" t="n">
-        <v>693.6400877573046</v>
+        <v>925.8297978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>1055.930629500164</v>
+        <v>1288.120339607742</v>
       </c>
       <c r="N24" t="n">
         <v>1465.420914107732</v>
@@ -6120,43 +6120,43 @@
         <v>428.7519797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>422.1497393251871</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>422.1497393251871</v>
+        <v>426.7510658086204</v>
       </c>
       <c r="F25" t="n">
-        <v>426.7207119171226</v>
+        <v>431.3220384005559</v>
       </c>
       <c r="G25" t="n">
-        <v>460.3372778040079</v>
+        <v>464.9386042874412</v>
       </c>
       <c r="H25" t="n">
-        <v>510.0638629634055</v>
+        <v>514.6651894468388</v>
       </c>
       <c r="I25" t="n">
-        <v>611.4067418994885</v>
+        <v>616.0080683829217</v>
       </c>
       <c r="J25" t="n">
-        <v>852.7004825519398</v>
+        <v>857.301809035373</v>
       </c>
       <c r="K25" t="n">
-        <v>852.7004825519398</v>
+        <v>857.301809035373</v>
       </c>
       <c r="L25" t="n">
-        <v>852.7004825519398</v>
+        <v>857.301809035373</v>
       </c>
       <c r="M25" t="n">
-        <v>852.7004825519398</v>
+        <v>857.301809035373</v>
       </c>
       <c r="N25" t="n">
-        <v>557.5640428835711</v>
+        <v>562.1653693670044</v>
       </c>
       <c r="O25" t="n">
-        <v>557.5640428835711</v>
+        <v>562.1653693670044</v>
       </c>
       <c r="P25" t="n">
-        <v>149.3356360634903</v>
+        <v>149.5917357020776</v>
       </c>
       <c r="Q25" t="n">
         <v>149.3356360634903</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>512.760190708043</v>
+        <v>430.2263084310288</v>
       </c>
       <c r="C26" t="n">
-        <v>428.4049367793326</v>
+        <v>430.2263084310288</v>
       </c>
       <c r="D26" t="n">
-        <v>428.4049367793326</v>
+        <v>243.0150400069381</v>
       </c>
       <c r="E26" t="n">
-        <v>428.4049367793326</v>
+        <v>61.84</v>
       </c>
       <c r="F26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6223,16 +6223,16 @@
         <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1928.125479385524</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>2438.974308114459</v>
+        <v>1274.910585172543</v>
       </c>
       <c r="N26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947306</v>
       </c>
       <c r="O26" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947306</v>
       </c>
       <c r="P26" t="n">
         <v>2653.400904947332</v>
@@ -6262,7 +6262,7 @@
         <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>689.8215740427202</v>
       </c>
     </row>
     <row r="27">
@@ -6293,25 +6293,25 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>69.63487796756496</v>
+        <v>61.84</v>
       </c>
       <c r="J27" t="n">
-        <v>416.3413981428639</v>
+        <v>408.546520175299</v>
       </c>
       <c r="K27" t="n">
-        <v>828.2842142372474</v>
+        <v>820.4893362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1314.589797864882</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.390920121557</v>
+        <v>1623.420339607742</v>
       </c>
       <c r="N27" t="n">
-        <v>1783.421204729126</v>
+        <v>1979.45062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2245.213656412845</v>
+        <v>2441.243075899029</v>
       </c>
       <c r="P27" t="n">
         <v>2580.493000882351</v>
@@ -6369,37 +6369,37 @@
         <v>175.5382646830375</v>
       </c>
       <c r="H28" t="n">
-        <v>171.7290463985742</v>
+        <v>175.5382646830375</v>
       </c>
       <c r="I28" t="n">
-        <v>219.6119253346571</v>
+        <v>223.4211436191204</v>
       </c>
       <c r="J28" t="n">
-        <v>407.4456659871084</v>
+        <v>411.2548842715717</v>
       </c>
       <c r="K28" t="n">
-        <v>407.4456659871084</v>
+        <v>411.2548842715717</v>
       </c>
       <c r="L28" t="n">
-        <v>407.4456659871084</v>
+        <v>411.2548842715717</v>
       </c>
       <c r="M28" t="n">
-        <v>407.4456659871084</v>
+        <v>411.2548842715717</v>
       </c>
       <c r="N28" t="n">
-        <v>407.4456659871084</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="O28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6430,16 +6430,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>835.7099373146964</v>
+        <v>1022.389550081067</v>
       </c>
       <c r="C29" t="n">
-        <v>608.9679390894501</v>
+        <v>795.6475518558203</v>
       </c>
       <c r="D29" t="n">
-        <v>608.9679390894501</v>
+        <v>608.4362834317296</v>
       </c>
       <c r="E29" t="n">
-        <v>608.9679390894501</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="F29" t="n">
         <v>427.2612434247916</v>
@@ -6454,22 +6454,22 @@
         <v>61.84</v>
       </c>
       <c r="J29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="K29" t="n">
-        <v>453.1491130376558</v>
+        <v>61.84</v>
       </c>
       <c r="L29" t="n">
-        <v>764.0617564435998</v>
+        <v>764.0617564436008</v>
       </c>
       <c r="M29" t="n">
-        <v>1274.910585172535</v>
+        <v>1274.910585172536</v>
       </c>
       <c r="N29" t="n">
-        <v>1888.130904947298</v>
+        <v>1888.130904947299</v>
       </c>
       <c r="O29" t="n">
-        <v>1888.130904947298</v>
+        <v>1888.130904947299</v>
       </c>
       <c r="P29" t="n">
         <v>2653.400904947332</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>2793.286094312508</v>
+        <v>3065.860001183541</v>
       </c>
       <c r="T29" t="n">
-        <v>2601.561807646623</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="U29" t="n">
-        <v>2173.055447496511</v>
+        <v>2700.531130750648</v>
       </c>
       <c r="V29" t="n">
-        <v>2173.055447496511</v>
+        <v>2291.590702299311</v>
       </c>
       <c r="W29" t="n">
-        <v>1755.50648185919</v>
+        <v>1874.04173666199</v>
       </c>
       <c r="X29" t="n">
-        <v>1384.514730888819</v>
+        <v>1503.049985691618</v>
       </c>
       <c r="Y29" t="n">
-        <v>1095.305202926388</v>
+        <v>1213.840457729188</v>
       </c>
     </row>
     <row r="30">
@@ -6533,25 +6533,25 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>416.3413981428639</v>
+        <v>212.5171006891147</v>
       </c>
       <c r="K30" t="n">
-        <v>828.2842142372474</v>
+        <v>624.4599167834981</v>
       </c>
       <c r="L30" t="n">
-        <v>1322.384675832448</v>
+        <v>1118.560378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1478.792447681983</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>1834.822732289551</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2296.61518397327</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
-        <v>2631.894528442776</v>
+        <v>2580.493000882351</v>
       </c>
       <c r="Q30" t="n">
         <v>2631.894528442776</v>
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>152.8679157637369</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="C31" t="n">
-        <v>152.8679157637369</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="D31" t="n">
-        <v>152.8679157637369</v>
+        <v>122.1955868066416</v>
       </c>
       <c r="E31" t="n">
-        <v>152.8679157637369</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="F31" t="n">
-        <v>152.8679157637369</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="G31" t="n">
-        <v>152.8679157637369</v>
+        <v>65.64921828446326</v>
       </c>
       <c r="H31" t="n">
-        <v>149.0586974792737</v>
+        <v>61.84</v>
       </c>
       <c r="I31" t="n">
-        <v>196.9415764153566</v>
+        <v>109.7228789360829</v>
       </c>
       <c r="J31" t="n">
-        <v>384.7753170678079</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="K31" t="n">
-        <v>384.7753170678079</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="L31" t="n">
-        <v>384.7753170678079</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="M31" t="n">
-        <v>384.7753170678079</v>
+        <v>297.5566195885342</v>
       </c>
       <c r="N31" t="n">
-        <v>384.7753170678079</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="O31" t="n">
-        <v>61.84</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="P31" t="n">
-        <v>61.84</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.84</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="R31" t="n">
-        <v>61.84</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="S31" t="n">
-        <v>61.84</v>
+        <v>69.64501712921572</v>
       </c>
       <c r="T31" t="n">
-        <v>76.66567915880486</v>
+        <v>84.47069628802058</v>
       </c>
       <c r="U31" t="n">
-        <v>149.9668717970915</v>
+        <v>157.7718889263072</v>
       </c>
       <c r="V31" t="n">
-        <v>175.5382646830375</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="W31" t="n">
-        <v>175.5382646830375</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="X31" t="n">
-        <v>152.8679157637369</v>
+        <v>183.3432818122532</v>
       </c>
       <c r="Y31" t="n">
-        <v>152.8679157637369</v>
+        <v>183.3432818122532</v>
       </c>
     </row>
     <row r="32">
@@ -6691,7 +6691,7 @@
         <v>61.84</v>
       </c>
       <c r="J32" t="n">
-        <v>445.5561922637025</v>
+        <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
         <v>810.0236653847963</v>
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1828.262200814254</v>
+        <v>368.1567292570302</v>
       </c>
       <c r="C33" t="n">
-        <v>1757.454208445042</v>
+        <v>297.3487368878188</v>
       </c>
       <c r="D33" t="n">
-        <v>1699.941393396858</v>
+        <v>239.8359218396343</v>
       </c>
       <c r="E33" t="n">
-        <v>1647.747355798967</v>
+        <v>187.6418842417428</v>
       </c>
       <c r="F33" t="n">
-        <v>1598.61983828596</v>
+        <v>138.5143667287359</v>
       </c>
       <c r="G33" t="n">
-        <v>1563.529398008154</v>
+        <v>103.4239264509305</v>
       </c>
       <c r="H33" t="n">
-        <v>1521.945471557224</v>
+        <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>1521.945471557224</v>
+        <v>61.84</v>
       </c>
       <c r="J33" t="n">
-        <v>1933.991991732523</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K33" t="n">
-        <v>2123.184807826906</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L33" t="n">
-        <v>2404.325849935922</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M33" t="n">
-        <v>2490.406391678781</v>
+        <v>732.4203396077418</v>
       </c>
       <c r="N33" t="n">
-        <v>2623.686676286349</v>
+        <v>1153.79062421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2862.729127970068</v>
+        <v>1392.833075899029</v>
       </c>
       <c r="P33" t="n">
-        <v>2975.258472439575</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
-        <v>3092</v>
+        <v>1631.894528442776</v>
       </c>
       <c r="R33" t="n">
-        <v>2833.137578492546</v>
+        <v>1373.032106935323</v>
       </c>
       <c r="S33" t="n">
-        <v>2655.800204790919</v>
+        <v>1195.694733233695</v>
       </c>
       <c r="T33" t="n">
-        <v>2540.287310631814</v>
+        <v>1080.18183907459</v>
       </c>
       <c r="U33" t="n">
-        <v>2429.973815924554</v>
+        <v>969.8683443673306</v>
       </c>
       <c r="V33" t="n">
-        <v>2305.21556623615</v>
+        <v>845.1100946789263</v>
       </c>
       <c r="W33" t="n">
-        <v>2162.414411781778</v>
+        <v>702.308940224554</v>
       </c>
       <c r="X33" t="n">
-        <v>2032.250028503609</v>
+        <v>572.1445569463848</v>
       </c>
       <c r="Y33" t="n">
-        <v>1922.763773184281</v>
+        <v>462.6583016270571</v>
       </c>
     </row>
     <row r="34">
@@ -6855,19 +6855,19 @@
         <v>1011.831843630726</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630726</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630726</v>
+        <v>745.3076490908711</v>
       </c>
       <c r="N34" t="n">
-        <v>728.8166160835699</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="O34" t="n">
-        <v>501.0715822480788</v>
+        <v>462.2924215437147</v>
       </c>
       <c r="P34" t="n">
-        <v>501.0715822480788</v>
+        <v>61.84</v>
       </c>
       <c r="Q34" t="n">
         <v>61.84</v>
@@ -6931,19 +6931,19 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.0181114556215</v>
+        <v>1155.056868702881</v>
       </c>
       <c r="L35" t="n">
-        <v>794.485584576666</v>
+        <v>1315.706713776682</v>
       </c>
       <c r="M35" t="n">
         <v>1300.1686329686</v>
       </c>
       <c r="N35" t="n">
-        <v>1910.301728341278</v>
+        <v>1910.301728341279</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533196</v>
+        <v>2675.571728341327</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -6952,7 +6952,7 @@
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S35" t="n">
         <v>2877.550748295214</v>
@@ -7007,25 +7007,25 @@
         <v>61.84</v>
       </c>
       <c r="J36" t="n">
-        <v>185.796520175299</v>
+        <v>195.5871006891145</v>
       </c>
       <c r="K36" t="n">
-        <v>374.9893362696823</v>
+        <v>384.7799167834979</v>
       </c>
       <c r="L36" t="n">
-        <v>646.3397978648825</v>
+        <v>656.130378378698</v>
       </c>
       <c r="M36" t="n">
-        <v>732.4203396077418</v>
+        <v>742.2109201215573</v>
       </c>
       <c r="N36" t="n">
-        <v>865.7006242153101</v>
+        <v>875.4912047291256</v>
       </c>
       <c r="O36" t="n">
-        <v>1231.27518397327</v>
+        <v>1114.533656412844</v>
       </c>
       <c r="P36" t="n">
-        <v>1631.894528442776</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7098,19 +7098,19 @@
         <v>1011.831843630703</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630703</v>
+        <v>728.8166160835463</v>
       </c>
       <c r="O37" t="n">
-        <v>658.8565263791725</v>
+        <v>728.8166160835463</v>
       </c>
       <c r="P37" t="n">
-        <v>258.4041048354578</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="Q37" t="n">
-        <v>258.4041048354578</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R37" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
-        <v>70.38201150041843</v>
+        <v>61.84</v>
       </c>
       <c r="I38" t="n">
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>61.84</v>
+        <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>771.3406764391725</v>
+        <v>654.8867607574211</v>
       </c>
       <c r="L38" t="n">
-        <v>1226.451937043414</v>
+        <v>1420.156760757421</v>
       </c>
       <c r="M38" t="n">
-        <v>1732.134985435348</v>
+        <v>1925.839809149355</v>
       </c>
       <c r="N38" t="n">
-        <v>2342.268080808026</v>
+        <v>1910.301728341273</v>
       </c>
       <c r="O38" t="n">
-        <v>2326.729999999944</v>
+        <v>1894.763647533191</v>
       </c>
       <c r="P38" t="n">
-        <v>3092</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7247,19 +7247,19 @@
         <v>185.796520175299</v>
       </c>
       <c r="K39" t="n">
-        <v>501.5214443439232</v>
+        <v>374.9893362696823</v>
       </c>
       <c r="L39" t="n">
-        <v>1060.961905939123</v>
+        <v>646.3397978648825</v>
       </c>
       <c r="M39" t="n">
-        <v>1147.042447681983</v>
+        <v>732.4203396077418</v>
       </c>
       <c r="N39" t="n">
-        <v>1280.322732289551</v>
+        <v>865.7006242153101</v>
       </c>
       <c r="O39" t="n">
-        <v>1519.36518397327</v>
+        <v>1231.27518397327</v>
       </c>
       <c r="P39" t="n">
         <v>1631.894528442776</v>
@@ -7332,22 +7332,22 @@
         <v>1011.83184363073</v>
       </c>
       <c r="M40" t="n">
-        <v>779.8807210018917</v>
+        <v>1011.83184363073</v>
       </c>
       <c r="N40" t="n">
-        <v>779.8807210018917</v>
+        <v>973.6184277340717</v>
       </c>
       <c r="O40" t="n">
-        <v>426.9054037503615</v>
+        <v>973.6184277340717</v>
       </c>
       <c r="P40" t="n">
-        <v>61.84</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="Q40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R40" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>144.0740160054425</v>
+        <v>889.6993585589771</v>
       </c>
       <c r="C41" t="n">
-        <v>61.84</v>
+        <v>650.8361482125185</v>
       </c>
       <c r="D41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="E41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="F41" t="n">
-        <v>61.84</v>
+        <v>451.5036676672158</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,52 +7402,52 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>1536.816366347868</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M41" t="n">
-        <v>2047.665195076803</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="N41" t="n">
-        <v>2326.729999999937</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="O41" t="n">
-        <v>3092</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="P41" t="n">
-        <v>3092</v>
+        <v>2693.395479385586</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3053.738789062329</v>
+        <v>3092</v>
       </c>
       <c r="S41" t="n">
-        <v>2769.043670070084</v>
+        <v>2807.304881007754</v>
       </c>
       <c r="T41" t="n">
-        <v>2391.593587515979</v>
+        <v>2429.854798453649</v>
       </c>
       <c r="U41" t="n">
-        <v>1950.966015244655</v>
+        <v>2429.854798453649</v>
       </c>
       <c r="V41" t="n">
-        <v>1529.904374672105</v>
+        <v>2275.52971722564</v>
       </c>
       <c r="W41" t="n">
-        <v>1100.234196913573</v>
+        <v>1845.859539467107</v>
       </c>
       <c r="X41" t="n">
-        <v>717.1212338219889</v>
+        <v>1462.746576375524</v>
       </c>
       <c r="Y41" t="n">
-        <v>415.7904937383461</v>
+        <v>1161.415836291881</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>560.3682724866701</v>
+        <v>840.8840019843029</v>
       </c>
       <c r="C42" t="n">
-        <v>410.7724013295799</v>
+        <v>691.2881308272127</v>
       </c>
       <c r="D42" t="n">
-        <v>410.7724013295799</v>
+        <v>554.9874369911495</v>
       </c>
       <c r="E42" t="n">
-        <v>410.7724013295799</v>
+        <v>424.0055206053792</v>
       </c>
       <c r="F42" t="n">
-        <v>282.8570050286942</v>
+        <v>296.0901243044934</v>
       </c>
       <c r="G42" t="n">
-        <v>186.379871795727</v>
+        <v>182.2118052388092</v>
       </c>
       <c r="H42" t="n">
-        <v>66.00806655691771</v>
+        <v>61.84</v>
       </c>
       <c r="I42" t="n">
         <v>61.84</v>
@@ -7496,37 +7496,37 @@
         <v>1920.05062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2170.276108733393</v>
+        <v>2369.963075899029</v>
       </c>
       <c r="P42" t="n">
-        <v>2493.6754532029</v>
+        <v>2492.008087641312</v>
       </c>
       <c r="Q42" t="n">
-        <v>2533.196980763325</v>
+        <v>2531.529615201737</v>
       </c>
       <c r="R42" t="n">
-        <v>2195.546680467992</v>
+        <v>2193.879314906404</v>
       </c>
       <c r="S42" t="n">
-        <v>1939.421427978486</v>
+        <v>1937.754062416898</v>
       </c>
       <c r="T42" t="n">
-        <v>1745.120655031502</v>
+        <v>1743.453289469915</v>
       </c>
       <c r="U42" t="n">
-        <v>1556.019281536364</v>
+        <v>1554.351915974776</v>
       </c>
       <c r="V42" t="n">
-        <v>1352.473153060081</v>
+        <v>1350.805787498493</v>
       </c>
       <c r="W42" t="n">
-        <v>1130.88411981783</v>
+        <v>1238.110398157557</v>
       </c>
       <c r="X42" t="n">
-        <v>921.9318577517822</v>
+        <v>1029.158136091509</v>
       </c>
       <c r="Y42" t="n">
-        <v>733.6577236445758</v>
+        <v>840.8840019843029</v>
       </c>
     </row>
     <row r="43">
@@ -7536,49 +7536,49 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="C43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="D43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="E43" t="n">
-        <v>61.84</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="F43" t="n">
-        <v>61.84</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="G43" t="n">
-        <v>61.84</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="H43" t="n">
-        <v>61.84</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="I43" t="n">
-        <v>97.84287893608291</v>
+        <v>162.393254893151</v>
       </c>
       <c r="J43" t="n">
-        <v>273.7966195885342</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="K43" t="n">
-        <v>273.7966195885342</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="L43" t="n">
-        <v>273.7966195885342</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="M43" t="n">
-        <v>273.7966195885342</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="N43" t="n">
-        <v>273.7966195885342</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="O43" t="n">
-        <v>61.84</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="P43" t="n">
-        <v>61.84</v>
+        <v>338.3469955456023</v>
       </c>
       <c r="Q43" t="n">
         <v>61.84</v>
@@ -7590,22 +7590,22 @@
         <v>61.84</v>
       </c>
       <c r="T43" t="n">
-        <v>61.84</v>
+        <v>64.78567915880487</v>
       </c>
       <c r="U43" t="n">
-        <v>123.2611926382866</v>
+        <v>126.2068717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>136.9525855242326</v>
+        <v>139.8982646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="X43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
       <c r="Y43" t="n">
-        <v>123.4446967982632</v>
+        <v>126.3903759570681</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>501.4894124392732</v>
+        <v>1211.157196550243</v>
       </c>
       <c r="C44" t="n">
-        <v>501.4894124392732</v>
+        <v>946.0313599411581</v>
       </c>
       <c r="D44" t="n">
-        <v>501.4894124392732</v>
+        <v>720.436253133229</v>
       </c>
       <c r="E44" t="n">
-        <v>281.9305340484968</v>
+        <v>500.8773747424526</v>
       </c>
       <c r="F44" t="n">
-        <v>61.84</v>
+        <v>280.7868406939558</v>
       </c>
       <c r="G44" t="n">
         <v>61.84</v>
@@ -7645,13 +7645,13 @@
         <v>1162.855479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>1529.331756443634</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>2040.180585172569</v>
+        <v>1673.704308114459</v>
       </c>
       <c r="N44" t="n">
-        <v>2653.400904947332</v>
+        <v>1888.130904947256</v>
       </c>
       <c r="O44" t="n">
         <v>2653.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3092</v>
       </c>
       <c r="R44" t="n">
-        <v>3092</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>3092</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="T44" t="n">
-        <v>2688.287291183269</v>
+        <v>2716.518417544831</v>
       </c>
       <c r="U44" t="n">
-        <v>2221.397092649318</v>
+        <v>2249.628219010881</v>
       </c>
       <c r="V44" t="n">
-        <v>1992.370276156441</v>
+        <v>1802.303952175705</v>
       </c>
       <c r="W44" t="n">
-        <v>1536.437472135282</v>
+        <v>1802.303952175705</v>
       </c>
       <c r="X44" t="n">
-        <v>1127.061882781072</v>
+        <v>1802.303952175705</v>
       </c>
       <c r="Y44" t="n">
-        <v>799.4685164348031</v>
+        <v>1474.710585829436</v>
       </c>
     </row>
     <row r="45">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>660.0379420416546</v>
+        <v>546.8962490198414</v>
       </c>
       <c r="C45" t="n">
-        <v>660.0379420416546</v>
+        <v>371.037751600125</v>
       </c>
       <c r="D45" t="n">
-        <v>660.0379420416546</v>
+        <v>208.4744315014355</v>
       </c>
       <c r="E45" t="n">
-        <v>502.793399393258</v>
+        <v>208.4744315014355</v>
       </c>
       <c r="F45" t="n">
-        <v>348.615376829746</v>
+        <v>208.4744315014355</v>
       </c>
       <c r="G45" t="n">
         <v>208.4744315014355</v>
@@ -7718,52 +7718,52 @@
         <v>61.84</v>
       </c>
       <c r="J45" t="n">
-        <v>370.9265201752989</v>
+        <v>185.796520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>745.2493362696823</v>
+        <v>560.1193362696824</v>
       </c>
       <c r="L45" t="n">
-        <v>1201.729797864882</v>
+        <v>1016.599797864882</v>
       </c>
       <c r="M45" t="n">
         <v>1287.810339607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1594.307441690021</v>
+        <v>1606.22062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>2018.47989337374</v>
+        <v>2015.28688947076</v>
       </c>
       <c r="P45" t="n">
-        <v>2316.139237843247</v>
+        <v>2312.946233940267</v>
       </c>
       <c r="Q45" t="n">
-        <v>2316.139237843247</v>
+        <v>2326.727761500692</v>
       </c>
       <c r="R45" t="n">
-        <v>1952.226311285287</v>
+        <v>1962.814834942733</v>
       </c>
       <c r="S45" t="n">
-        <v>1802.814004741713</v>
+        <v>1680.4269561906</v>
       </c>
       <c r="T45" t="n">
-        <v>1802.814004741713</v>
+        <v>1459.86355698099</v>
       </c>
       <c r="U45" t="n">
-        <v>1587.450004983948</v>
+        <v>1244.499557223226</v>
       </c>
       <c r="V45" t="n">
-        <v>1357.641250245039</v>
+        <v>1244.499557223226</v>
       </c>
       <c r="W45" t="n">
-        <v>1109.789590740162</v>
+        <v>996.6478977183484</v>
       </c>
       <c r="X45" t="n">
-        <v>874.5747024114872</v>
+        <v>761.4330093896741</v>
       </c>
       <c r="Y45" t="n">
-        <v>660.0379420416546</v>
+        <v>546.8962490198414</v>
       </c>
     </row>
     <row r="46">
@@ -7797,40 +7797,40 @@
         <v>72.10287893608292</v>
       </c>
       <c r="J46" t="n">
-        <v>222.3166195885343</v>
+        <v>203.6102277937148</v>
       </c>
       <c r="K46" t="n">
-        <v>222.3166195885343</v>
+        <v>203.6102277937148</v>
       </c>
       <c r="L46" t="n">
-        <v>222.3166195885343</v>
+        <v>203.6102277937148</v>
       </c>
       <c r="M46" t="n">
-        <v>222.3166195885343</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="N46" t="n">
-        <v>222.3166195885343</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="O46" t="n">
-        <v>222.3166195885343</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="P46" t="n">
-        <v>222.3166195885343</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="Q46" t="n">
-        <v>68.35186403001501</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="R46" t="n">
-        <v>68.35186403001501</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="S46" t="n">
-        <v>68.35186403001501</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="T46" t="n">
-        <v>68.35186403001501</v>
+        <v>80.64510667265762</v>
       </c>
       <c r="U46" t="n">
-        <v>104.0330566683016</v>
+        <v>116.3262993109443</v>
       </c>
       <c r="V46" t="n">
         <v>104.0330566683016</v>
@@ -7970,16 +7970,16 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>306.2599628088302</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>884.2478695740924</v>
+        <v>571.0933679639695</v>
       </c>
       <c r="P2" t="n">
         <v>814.2870600406815</v>
@@ -8204,25 +8204,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>629.6852052399809</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>571.0933679639695</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>189.0212843274853</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,7 +8441,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>500.8454983898731</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406860149</v>
+        <v>598.2574409074598</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8681,13 +8681,13 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>161.5508809199773</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
         <v>70.24786957409245</v>
@@ -8696,7 +8696,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P14" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>334.3735652474629</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P17" t="n">
-        <v>532.8085520185707</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9389,19 +9389,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>681.6676550513207</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>884.2478695740924</v>
+        <v>110.1927438789493</v>
       </c>
       <c r="P20" t="n">
         <v>814.2870600406815</v>
@@ -9626,7 +9626,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>64.42599844307665</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,16 +9635,16 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>815.1849144666769</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P23" t="n">
         <v>814.2870600406815</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,19 +9866,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>657.4491031847606</v>
       </c>
       <c r="N26" t="n">
-        <v>693.8414801232425</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407081</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>314.0531751575193</v>
+        <v>709.3149054985868</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10115,7 +10115,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>773.2870600407163</v>
+        <v>773.2870600407153</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10337,7 +10337,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>375.292246238201</v>
+        <v>375.2922462382009</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>375.292246238147</v>
+        <v>174.4260466230627</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407308</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>50.42570624509142</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>716.8751175230994</v>
+        <v>221.7067106570983</v>
       </c>
       <c r="L38" t="n">
-        <v>465.9428479981992</v>
+        <v>773</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407381</v>
+        <v>773.2870600407372</v>
       </c>
       <c r="Q38" t="n">
-        <v>188.2053843274866</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>759.1325994063338</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>843.2478695741563</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407444</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>575.4535132309335</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11288,16 +11288,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>693.841480123165</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>843.24786957417</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -22703,7 +22703,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696446828</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>5.662449696445606</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,10 +22937,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.66244969644795</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>29.21007785422734</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23177,7 +23177,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>29.21007785422739</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785422643</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23229,13 +23229,13 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -23271,28 +23271,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>55.40484126645407</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>73.20896483131551</v>
       </c>
     </row>
     <row r="12">
@@ -23396,10 +23396,10 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23420,7 +23420,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>133.362991338331</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
@@ -23429,7 +23429,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>179.4963914954437</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23444,13 +23444,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>62.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23517,13 +23517,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>392.4306086145859</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>5.057132633637991</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23624,7 +23624,7 @@
         <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>34.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>29.98090483695654</v>
@@ -23651,22 +23651,22 @@
         <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
         <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>371.0033629600134</v>
       </c>
       <c r="P16" t="n">
-        <v>177.4989615751193</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
         <v>474.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23855,13 +23855,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>1.98090483695654</v>
@@ -23894,16 +23894,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>85.62542115844059</v>
       </c>
       <c r="R19" t="n">
-        <v>437.7909116620232</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24003,7 +24003,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.43060861457991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24122,16 +24122,16 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L22" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>259.1932569882871</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
@@ -24140,7 +24140,7 @@
         <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>278.5513985762656</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -24177,7 +24177,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4306086145781762</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24335,10 +24335,10 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24371,10 +24371,10 @@
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>4.30177457639752</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>446.5857277833966</v>
       </c>
       <c r="R25" t="n">
         <v>447.6021279811511</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>140.9628768535707</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>175.2907695013304</v>
       </c>
     </row>
     <row r="27">
@@ -24584,7 +24584,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24602,10 +24602,10 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>137.6378195456844</v>
       </c>
       <c r="O28" t="n">
-        <v>73.29595475177763</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24617,7 +24617,7 @@
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24645,19 +24645,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>67.46291438393487</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -24696,16 +24696,16 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>171.8685379293374</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V29" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -24809,10 +24809,10 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>49.38285596774193</v>
@@ -24839,10 +24839,10 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>120.5525888369596</v>
       </c>
       <c r="O31" t="n">
-        <v>95.73960018188518</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
         <v>462.4478973282775</v>
@@ -24869,7 +24869,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
         <v>62.46535284946236</v>
@@ -25070,22 +25070,22 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>229.6316114025499</v>
+        <v>98.32028696587227</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>123.9779805818788</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
         <v>435.6021279811511</v>
@@ -25313,22 +25313,22 @@
         <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>242.3537935340202</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>241.0036641940478</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25547,25 +25547,25 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>242.3537935339931</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>35.03314761541958</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,10 +25596,10 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>155.0629023976059</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>197.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>191.3632896068686</v>
@@ -25608,10 +25608,10 @@
         <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>264.0691937510946</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25672,28 +25672,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>171.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>134.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>129.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>17.2271739743898</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4.126385891348534</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>107.8047074623018</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25760,7 +25760,7 @@
         <v>72.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>6.992255006675947</v>
+        <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
         <v>61.38285596774193</v>
@@ -25790,13 +25790,13 @@
         <v>358.1850752716849</v>
       </c>
       <c r="O43" t="n">
-        <v>217.6085106863661</v>
+        <v>427.445564079015</v>
       </c>
       <c r="P43" t="n">
         <v>474.4478973282775</v>
       </c>
       <c r="Q43" t="n">
-        <v>512.839266425598</v>
+        <v>239.0973408354517</v>
       </c>
       <c r="R43" t="n">
         <v>513.6021279811511</v>
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>34.08145756917327</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>223.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>216.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>221.0096587035274</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>63.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>399.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>216.1144758388754</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>405.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25912,19 +25912,19 @@
         <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>174.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -25960,16 +25960,16 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>131.6458164864724</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>218.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -26021,7 +26021,7 @@
         <v>236.5476281577792</v>
       </c>
       <c r="M46" t="n">
-        <v>333.6316114025499</v>
+        <v>211.8961414927033</v>
       </c>
       <c r="N46" t="n">
         <v>384.1850752716849</v>
@@ -26033,7 +26033,7 @@
         <v>500.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>386.4141584226639</v>
+        <v>538.839266425598</v>
       </c>
       <c r="R46" t="n">
         <v>539.6021279811511</v>
@@ -26048,7 +26048,7 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>39.37280983870968</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>901034.6564785377</v>
+        <v>901034.6564785378</v>
       </c>
     </row>
     <row r="3">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4671417.06822837</v>
+        <v>4671417.068228371</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5433389.563590955</v>
+        <v>5433389.563590957</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6888306.765557615</v>
+        <v>6888306.765557617</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7584159.04307078</v>
+        <v>7584159.043070783</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8351522.774164387</v>
+        <v>8351522.774164388</v>
       </c>
     </row>
     <row r="13">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9884056.652825503</v>
+        <v>9884056.652825501</v>
       </c>
     </row>
     <row r="15">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11187716.4234181</v>
+        <v>11187716.42341809</v>
       </c>
     </row>
   </sheetData>
@@ -26293,7 +26293,7 @@
         <v>1371550.491652661</v>
       </c>
       <c r="J2" t="n">
-        <v>1252534.099523704</v>
+        <v>1252534.099523703</v>
       </c>
       <c r="K2" t="n">
         <v>1252534.099523703</v>
@@ -26305,7 +26305,7 @@
         <v>1379280.490794997</v>
       </c>
       <c r="N2" t="n">
-        <v>1379280.490794999</v>
+        <v>1379280.490794998</v>
       </c>
       <c r="O2" t="n">
         <v>1215148.976618704</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.1964558328</v>
+        <v>551386.5909530219</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165733</v>
+        <v>549634.6822137623</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037627</v>
+        <v>547880.3969009516</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682167</v>
+        <v>494181.551669461</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925398</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.0458524429</v>
+        <v>517298.0248536869</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.7754680162</v>
+        <v>515622.7544692601</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335261</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795845</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.9144927664</v>
+        <v>519822.4908174388</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912134</v>
+        <v>518092.3721158857</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666617</v>
+        <v>516359.765791334</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.0841633691</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682331</v>
+        <v>393445.3182115989</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>490139.5018162728</v>
+        <v>494977.1073190839</v>
       </c>
       <c r="C6" t="n">
-        <v>778419.4105555324</v>
+        <v>783257.0160583432</v>
       </c>
       <c r="D6" t="n">
-        <v>780173.6958683429</v>
+        <v>785011.3013711539</v>
       </c>
       <c r="E6" t="n">
-        <v>543680.9688894824</v>
+        <v>548468.9898882379</v>
       </c>
       <c r="F6" t="n">
-        <v>728082.0518009091</v>
+        <v>732870.072799665</v>
       </c>
       <c r="G6" t="n">
-        <v>752445.0598601208</v>
+        <v>757233.0808588769</v>
       </c>
       <c r="H6" t="n">
-        <v>776517.9948002181</v>
+        <v>781306.015798974</v>
       </c>
       <c r="I6" t="n">
-        <v>778193.2651846453</v>
+        <v>782981.2861834007</v>
       </c>
       <c r="J6" t="n">
-        <v>313354.5619901774</v>
+        <v>318019.5905468112</v>
       </c>
       <c r="K6" t="n">
-        <v>702915.3036441186</v>
+        <v>707580.3322007533</v>
       </c>
       <c r="L6" t="n">
-        <v>708084.0973022315</v>
+        <v>712795.5209775588</v>
       </c>
       <c r="M6" t="n">
-        <v>785014.2160037837</v>
+        <v>789725.6396791115</v>
       </c>
       <c r="N6" t="n">
-        <v>786746.8223283368</v>
+        <v>791458.2460036643</v>
       </c>
       <c r="O6" t="n">
-        <v>636927.7954553353</v>
+        <v>641592.8240119689</v>
       </c>
       <c r="P6" t="n">
-        <v>672583.1858532079</v>
+        <v>677248.2144098426</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27433,7 +27433,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>307.3903671255649</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
@@ -27451,49 +27451,49 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
+        <v>307.3903671255649</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>400</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>106.7298411717629</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>17.3083845693742</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27597,13 +27597,13 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E4" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F4" t="n">
         <v>400</v>
-      </c>
-      <c r="E4" t="n">
-        <v>400</v>
-      </c>
-      <c r="F4" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27615,7 +27615,7 @@
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>235.7909176872596</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27645,13 +27645,13 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U4" t="n">
         <v>400</v>
       </c>
-      <c r="U4" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>335.9571897604617</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27673,25 +27673,25 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>56.51176829727029</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>306.4306086145856</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27736,7 +27736,7 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>400</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>342.2743756165772</v>
+        <v>76.45355315257621</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,31 +27828,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
         <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>127.1886836637919</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27882,7 +27882,7 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>289.9338593164129</v>
       </c>
       <c r="U7" t="n">
         <v>150.9583912744579</v>
@@ -27891,10 +27891,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>287.4653528494624</v>
@@ -27907,28 +27907,28 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
         <v>400</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>56.51176829727007</v>
-      </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>400</v>
+        <v>306.4306086145853</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27961,7 +27961,7 @@
         <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27973,7 +27973,7 @@
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27998,10 +27998,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>207.6501538294816</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28040,19 +28040,19 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>400</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
         <v>400</v>
       </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28071,10 +28071,10 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>301.1842533366689</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
@@ -28083,16 +28083,16 @@
         <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="K10" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>279.1361586332916</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V10" t="n">
         <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28259,16 +28259,16 @@
         <v>225</v>
       </c>
       <c r="N12" t="n">
-        <v>26.99048536749049</v>
+        <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>71.03760616835913</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28484,13 +28484,13 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>166.1982915220774</v>
+        <v>244.1190264315981</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
@@ -28502,10 +28502,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>251</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>251</v>
@@ -28721,13 +28721,13 @@
         <v>279</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>279</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>261.5913251766237</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -28739,10 +28739,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>155.6705902671034</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>279</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28924,7 +28924,7 @@
         <v>279</v>
       </c>
       <c r="Y20" t="n">
-        <v>279.000000000006</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21">
@@ -28955,14 +28955,14 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>261.5913251766235</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>279</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
@@ -28973,13 +28973,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>279</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>217.5442043757548</v>
       </c>
       <c r="R21" t="n">
         <v>279</v>
@@ -29098,7 +29098,7 @@
         <v>279</v>
       </c>
       <c r="D23" t="n">
-        <v>279.0000000000078</v>
+        <v>279</v>
       </c>
       <c r="E23" t="n">
         <v>279</v>
@@ -29192,13 +29192,13 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>261.5913251766235</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29207,7 +29207,7 @@
         <v>279</v>
       </c>
       <c r="N24" t="n">
-        <v>279</v>
+        <v>44.46493928527497</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -29429,7 +29429,7 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>225</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>225</v>
@@ -29438,7 +29438,7 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29450,7 +29450,7 @@
         <v>225</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>26.99048536749045</v>
       </c>
       <c r="Q27" t="n">
         <v>225</v>
@@ -29669,7 +29669,7 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>225</v>
+        <v>19.11687125883917</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29678,7 +29678,7 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>71.03760616835939</v>
+        <v>225</v>
       </c>
       <c r="N30" t="n">
         <v>225</v>
@@ -29690,7 +29690,7 @@
         <v>225</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R30" t="n">
         <v>225</v>
@@ -29906,25 +29906,25 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>291</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>9.889475266480588</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>9.889475266480062</v>
       </c>
       <c r="Q33" t="n">
         <v>291</v>
@@ -30088,10 +30088,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>291</v>
+        <v>282.5434086145851</v>
       </c>
       <c r="T35" t="n">
         <v>291</v>
@@ -30143,7 +30143,7 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>9.889475266480332</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -30158,13 +30158,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>127.8102101760008</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>291</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>291</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30298,7 +30298,7 @@
         <v>291</v>
       </c>
       <c r="I38" t="n">
-        <v>141.6245682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30383,22 +30383,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>127.8102101760009</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>127.8102101760008</v>
+      </c>
+      <c r="P39" t="n">
         <v>291</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>173.0792650904796</v>
@@ -30632,10 +30632,10 @@
         <v>213</v>
       </c>
       <c r="O42" t="n">
-        <v>11.29599276198445</v>
+        <v>213</v>
       </c>
       <c r="P42" t="n">
-        <v>213</v>
+        <v>9.611785124016606</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30726,7 +30726,7 @@
         <v>213</v>
       </c>
       <c r="T43" t="n">
-        <v>210.0245665062577</v>
+        <v>213</v>
       </c>
       <c r="U43" t="n">
         <v>213</v>
@@ -30854,7 +30854,7 @@
         <v>187</v>
       </c>
       <c r="J45" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>187</v>
@@ -30863,19 +30863,19 @@
         <v>187</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="N45" t="n">
-        <v>174.966482297688</v>
+        <v>187</v>
       </c>
       <c r="O45" t="n">
-        <v>187</v>
+        <v>171.7412258300311</v>
       </c>
       <c r="P45" t="n">
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>187</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>187</v>
       </c>
       <c r="J46" t="n">
-        <v>187</v>
+        <v>168.1046547527076</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34883,13 +34883,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.95612715847</v>
@@ -34901,7 +34901,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>200.5219688513519</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>111.479226198857</v>
@@ -34931,13 +34931,13 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>136.7868795442455</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34946,7 +34946,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -35114,31 +35114,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>91.91973482788414</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35168,7 +35168,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>189.9754334937423</v>
+        <v>79.90929281015514</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -35177,10 +35177,10 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35235,7 +35235,7 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
         <v>814</v>
@@ -35357,10 +35357,10 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>15.64803528111344</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
@@ -35369,16 +35369,16 @@
         <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>69.11159212703393</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,13 +35460,13 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>161.5508809199773</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -35475,7 +35475,7 @@
         <v>814</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35545,16 +35545,16 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
-        <v>161.6170354761453</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>312.4946280711055</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P14" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>161.5508809199775</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,13 +35770,13 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>291.4068977597531</v>
+        <v>369.3276326692738</v>
       </c>
       <c r="K15" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
@@ -35788,10 +35788,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>364.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>77.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P17" t="n">
-        <v>532.5214919778892</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36007,13 +36007,13 @@
         <v>61.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>535.6827005253106</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
         <v>86.95004216450428</v>
@@ -36025,10 +36025,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>269.3365947817566</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,19 +36168,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
-        <v>137.4055274090034</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>814</v>
+        <v>39.94487430485688</v>
       </c>
       <c r="P20" t="n">
         <v>814</v>
@@ -36241,13 +36241,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>44.46493928527498</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>404.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
@@ -36259,13 +36259,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>44.46493928527515</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,7 +36405,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>64.42599844307665</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -36414,16 +36414,16 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>337.9359563968417</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P23" t="n">
         <v>814</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,13 +36478,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>44.46493928527492</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36493,7 +36493,7 @@
         <v>365.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>413.6265501086548</v>
+        <v>179.0914893939298</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
@@ -36645,19 +36645,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>773</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>113.1869755424433</v>
       </c>
       <c r="N26" t="n">
-        <v>216.5925220534073</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>773.0000000000266</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7.873614108651466</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>350.2086062376757</v>
@@ -36724,7 +36724,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>293.2082466075261</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36736,7 +36736,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>140.6564898821437</v>
       </c>
       <c r="Q27" t="n">
         <v>51.92073490952041</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>314.0531751575193</v>
+        <v>709.3149054985868</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36894,7 +36894,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>773.0000000000348</v>
+        <v>773.0000000000339</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,7 +36955,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36964,7 +36964,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>157.9876483328637</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
         <v>359.6265501086548</v>
@@ -36976,7 +36976,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320762831</v>
+        <v>727.1079320762801</v>
       </c>
       <c r="L32" t="n">
         <v>773</v>
       </c>
       <c r="M32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="O32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="P32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="Q32" t="n">
-        <v>773.0000000000421</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>416.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
         <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
-        <v>283.9808506151675</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
       </c>
       <c r="N33" t="n">
-        <v>134.6265501086548</v>
+        <v>425.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>113.6660045146532</v>
+        <v>123.5554797811333</v>
       </c>
       <c r="Q33" t="n">
         <v>117.9207349095204</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
+        <v>727.1079320759941</v>
+      </c>
+      <c r="L35" t="n">
         <v>773</v>
       </c>
-      <c r="L35" t="n">
-        <v>727.1079320760191</v>
-      </c>
       <c r="M35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="N35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="O35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="Q35" t="n">
-        <v>773.0000000000493</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37429,7 +37429,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>125.2086062376757</v>
+        <v>135.098081504156</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37444,13 +37444,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>369.2672320787472</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
         <v>404.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320763076</v>
+        <v>727.1079320762078</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
       </c>
       <c r="M38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="N38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="Q38" t="n">
-        <v>773.0000000000566</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37669,10 +37669,10 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>318.9140648167922</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>565.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
@@ -37681,10 +37681,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>241.4570219027464</v>
+        <v>369.2672320787472</v>
       </c>
       <c r="P39" t="n">
-        <v>113.6660045146532</v>
+        <v>404.6660045146532</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>772.9999999999999</v>
+        <v>773</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>281.8836413364986</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>773.0000000000639</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.000000000063</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>402.630828903448</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37918,10 +37918,10 @@
         <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>252.7530146647308</v>
+        <v>454.4570219027464</v>
       </c>
       <c r="P42" t="n">
-        <v>326.6660045146532</v>
+        <v>123.2777896386698</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.975433493742287</v>
       </c>
       <c r="U43" t="n">
         <v>62.04160872554206</v>
@@ -38067,16 +38067,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>370.1780576344547</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>216.5925220533296</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>773.0000000000775</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38140,7 +38140,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>312.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K45" t="n">
         <v>378.1038546407913</v>
@@ -38149,19 +38149,19 @@
         <v>461.091375348687</v>
       </c>
       <c r="M45" t="n">
-        <v>86.95004216450428</v>
+        <v>273.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>309.5930324063428</v>
+        <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>428.4570219027464</v>
+        <v>413.1982477327775</v>
       </c>
       <c r="P45" t="n">
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>13.92073490952041</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38219,7 +38219,7 @@
         <v>10.36654437988173</v>
       </c>
       <c r="J46" t="n">
-        <v>151.7310511640922</v>
+        <v>132.8357059167999</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
